--- a/cviceni/faktury-kontrola/data/objednavky.xlsx
+++ b/cviceni/faktury-kontrola/data/objednavky.xlsx
@@ -7,7 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Objednávky" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stavebniny Morava" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nářadí Profi" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Elektro Dvořák" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VTS Technik" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Barvy Piekarová" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +29,22 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +59,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,114 +428,518 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Soubor</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Datum přijetí</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Číslo faktury</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>IČO</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Číslo objednávky</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Dodavatel</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Schválená částka bez DPH</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Středisko</t>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Základ daně</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Splatnost</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Kompletní</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>2026-09-01_stavebniny-morava.pdf</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1. 9. 2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>FA-2026-0918</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>27182934</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>OBJ-2026-0442</t>
         </is>
       </c>
+      <c r="F2" t="n">
+        <v>48250</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>22. 9. 2026</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>ano</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Soubor</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Datum přijetí</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Číslo faktury</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>IČO</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Číslo objednávky</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Základ daně</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Splatnost</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Kompletní</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-09-02_naradi-profi.pdf</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Stavebniny Morava s.r.o.</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>48250</v>
+          <t>2. 9. 2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>FA-2026-0919</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CS Nehvizdy</t>
+          <t>45319876</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>OBJ-2026-0447</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>12900</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>25. 9. 2026</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>ano</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>OBJ-2026-0447</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Nářadí Profi a.s.</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>12900</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Divize Nářadí</t>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Soubor</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Datum přijetí</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Číslo faktury</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>IČO</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Číslo objednávky</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Základ daně</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Splatnost</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Kompletní</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03_elektro-dvorak.pdf</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>3. 9. 2026</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>2026/1044</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>61234567</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="n">
+        <v>7340</v>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>30. 9. 2026</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Soubor</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Datum přijetí</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Číslo faktury</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>IČO</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Číslo objednávky</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Základ daně</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Splatnost</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Kompletní</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-09-04_vts-technik.pdf</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>4. 9. 2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>FA-2026-0921</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>28374651</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>OBJ-2026-0451</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>VTS Technik s.r.o.</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>31900</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Divize VTS</t>
+      <c r="F2" t="n">
+        <v>33100</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>28. 9. 2026</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>ano</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>OBJ-2026-0455</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Elektro Dvořák s.r.o.</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>9900</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Divize Elektro</t>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Soubor</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Datum přijetí</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Číslo faktury</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>IČO</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Číslo objednávky</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Základ daně</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Splatnost</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Kompletní</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-09-05_barvy-piekarova.pdf</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>5. 9. 2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>FA-2026-0922</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>49876123</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>OBJ-9999-0001</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>5480</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>1. 10. 2026</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>ano</t>
         </is>
       </c>
     </row>

--- a/cviceni/faktury-kontrola/data/objednavky.xlsx
+++ b/cviceni/faktury-kontrola/data/objednavky.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stavebniny Morava" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nářadí Profi" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Elektro Dvořák" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VTS Technik" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Barvy Piekarová" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Stavebniny Morava" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Nářadí Profi" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Elektro Dvořák" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="VTS Technik" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Barvy Piekarová" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -439,6 +439,7 @@
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -480,6 +481,11 @@
       <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Kompletní</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Žádost odeslána</t>
         </is>
       </c>
     </row>
@@ -534,7 +540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -545,6 +551,7 @@
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -586,6 +593,11 @@
       <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Kompletní</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Žádost odeslána</t>
         </is>
       </c>
     </row>
@@ -640,7 +652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -651,6 +663,7 @@
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -694,6 +707,11 @@
           <t>Kompletní</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Žádost odeslána</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -728,6 +746,11 @@
       <c r="H2" s="2" t="inlineStr">
         <is>
           <t>ne</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>připraveno, čeká na konektor</t>
         </is>
       </c>
     </row>
@@ -742,7 +765,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -753,6 +776,7 @@
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -794,6 +818,11 @@
       <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Kompletní</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Žádost odeslána</t>
         </is>
       </c>
     </row>
@@ -848,7 +877,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -859,6 +888,7 @@
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -900,6 +930,11 @@
       <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Kompletní</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Žádost odeslána</t>
         </is>
       </c>
     </row>

--- a/cviceni/faktury-kontrola/data/objednavky.xlsx
+++ b/cviceni/faktury-kontrola/data/objednavky.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -489,46 +489,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-09-01_stavebniny-morava.pdf</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>1. 9. 2026</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>FA-2026-0918</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>27182934</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>OBJ-2026-0442</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>48250</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>22. 9. 2026</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -540,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -601,46 +561,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-09-02_naradi-profi.pdf</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2. 9. 2026</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>FA-2026-0919</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>45319876</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>OBJ-2026-0447</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>12900</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>25. 9. 2026</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -652,7 +572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -713,47 +633,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-03_elektro-dvorak.pdf</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>3. 9. 2026</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>2026/1044</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>61234567</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="n">
-        <v>7340</v>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>30. 9. 2026</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>ne</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>připraveno, čeká na konektor</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -765,7 +644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -826,46 +705,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-09-04_vts-technik.pdf</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>4. 9. 2026</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>FA-2026-0921</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>28374651</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>OBJ-2026-0451</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>33100</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>28. 9. 2026</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -877,7 +716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -938,46 +777,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-09-05_barvy-piekarova.pdf</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>5. 9. 2026</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>FA-2026-0922</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>49876123</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>OBJ-9999-0001</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>5480</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>1. 10. 2026</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cviceni/faktury-kontrola/data/objednavky.xlsx
+++ b/cviceni/faktury-kontrola/data/objednavky.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="5115" yWindow="855" windowWidth="21600" windowHeight="11295" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Stavebniny Morava" sheetId="1" state="visible" r:id="rId1"/>
@@ -14,7 +13,7 @@
     <sheet name="Barvy Piekarová" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -30,21 +29,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -62,10 +57,10 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normální" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -431,14 +426,7 @@
   <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="1" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -503,14 +491,7 @@
   <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="1" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -575,14 +556,7 @@
   <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="1" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -647,14 +621,7 @@
   <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="1" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -719,14 +686,7 @@
   <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="1" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>

--- a/cviceni/faktury-kontrola/data/objednavky.xlsx
+++ b/cviceni/faktury-kontrola/data/objednavky.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="5115" yWindow="855" windowWidth="21600" windowHeight="11295" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Stavebniny Morava" sheetId="1" state="visible" r:id="rId1"/>
@@ -13,7 +13,7 @@
     <sheet name="Barvy Piekarová" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -54,15 +54,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normální" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -424,7 +423,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
@@ -489,7 +488,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
@@ -554,7 +553,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
@@ -619,7 +618,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
@@ -684,7 +683,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
